--- a/BBC_Master.xlsx
+++ b/BBC_Master.xlsx
@@ -1,43 +1,159 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\6c7dda8d-47d4-4239-a00f-bdb51e8f6d86\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926A485B-46E7-4369-8620-D94021E83722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+  <si>
+    <t>BBC Name</t>
+  </si>
+  <si>
+    <t>DE / Manager</t>
+  </si>
+  <si>
+    <t>Area / TIP</t>
+  </si>
+  <si>
+    <t>Monthly Target</t>
+  </si>
+  <si>
+    <t>Manager Target</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>BHIKSHAPATHI MANCHALA</t>
+  </si>
+  <si>
+    <t>MAHESHWARAPU RANJITH KUMAR-KZP</t>
+  </si>
+  <si>
+    <t>CH MADHUKAR RAO</t>
+  </si>
+  <si>
+    <t>MAHESHWARAPU RANJITH KUMAR-WDP</t>
+  </si>
+  <si>
+    <t>SPANDANA T</t>
+  </si>
+  <si>
+    <t>KIRAN KUMAR ENUGULA</t>
+  </si>
+  <si>
+    <t>VINEETH GUNTI</t>
+  </si>
+  <si>
+    <t>VIKRAM NALLA</t>
+  </si>
+  <si>
+    <t>A PRAVEEN-JAN</t>
+  </si>
+  <si>
+    <t>A PRAVEEN-CHR</t>
+  </si>
+  <si>
+    <t>M RAMMOHAN</t>
+  </si>
+  <si>
+    <t>B SESHU SRINIVAS</t>
+  </si>
+  <si>
+    <t>G DAYAKAR</t>
+  </si>
+  <si>
+    <t>HNK</t>
+  </si>
+  <si>
+    <t>KZP</t>
+  </si>
+  <si>
+    <t>WGL</t>
+  </si>
+  <si>
+    <t>WDP</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>PKA &amp; BHPL</t>
+  </si>
+  <si>
+    <t>MLG</t>
+  </si>
+  <si>
+    <t>MBB &amp; DRNKL</t>
+  </si>
+  <si>
+    <t>THR</t>
+  </si>
+  <si>
+    <t>JAN</t>
+  </si>
+  <si>
+    <t>CHR</t>
+  </si>
+  <si>
+    <t>SURENDER GUGULOTH</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -46,100 +162,78 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +271,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -211,6 +305,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,9 +340,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -420,37 +516,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BBC Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>DE / Manager</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Area / TIP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Monthly Target</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4">
+        <v>87</v>
+      </c>
+      <c r="E2" s="4">
+        <v>225</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5">
+        <v>225</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4">
+        <v>225</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5">
+        <v>34</v>
+      </c>
+      <c r="E5" s="5">
+        <v>225</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4">
+        <v>125</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5">
+        <v>47</v>
+      </c>
+      <c r="E7" s="5">
+        <v>125</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <v>40</v>
+      </c>
+      <c r="E8" s="4">
+        <v>125</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="5">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5">
+        <v>120</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="4">
+        <v>25</v>
+      </c>
+      <c r="E10" s="4">
+        <v>120</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5">
+        <v>44</v>
+      </c>
+      <c r="E11" s="5">
+        <v>120</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4">
+        <v>17</v>
+      </c>
+      <c r="E12" s="4">
+        <v>120</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/BBC_Master.xlsx
+++ b/BBC_Master.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\6c7dda8d-47d4-4239-a00f-bdb51e8f6d86\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926A485B-46E7-4369-8620-D94021E83722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>BBC Name</t>
   </si>
@@ -43,9 +37,6 @@
     <t>S.No</t>
   </si>
   <si>
-    <t>BHIKSHAPATHI MANCHALA</t>
-  </si>
-  <si>
     <t>MAHESHWARAPU RANJITH KUMAR-KZP</t>
   </si>
   <si>
@@ -67,12 +58,6 @@
     <t>VIKRAM NALLA</t>
   </si>
   <si>
-    <t>A PRAVEEN-JAN</t>
-  </si>
-  <si>
-    <t>A PRAVEEN-CHR</t>
-  </si>
-  <si>
     <t>M RAMMOHAN</t>
   </si>
   <si>
@@ -109,20 +94,23 @@
     <t>THR</t>
   </si>
   <si>
-    <t>JAN</t>
-  </si>
-  <si>
-    <t>CHR</t>
-  </si>
-  <si>
     <t>SURENDER GUGULOTH</t>
+  </si>
+  <si>
+    <t>MOHAMMAD SHAFEEQ</t>
+  </si>
+  <si>
+    <t>JAN &amp; CHR</t>
+  </si>
+  <si>
+    <t>KIRAN NATTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -271,7 +259,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -305,7 +293,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -340,10 +327,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -516,20 +502,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,15 +538,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="D2" s="4">
         <v>87</v>
@@ -572,15 +558,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5">
         <v>40</v>
@@ -592,15 +578,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4">
         <v>64</v>
@@ -612,15 +598,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5">
         <v>34</v>
@@ -632,15 +618,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4">
         <v>38</v>
@@ -652,15 +638,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5">
         <v>47</v>
@@ -672,15 +658,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4">
         <v>40</v>
@@ -692,15 +678,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5">
         <v>34</v>
@@ -712,15 +698,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4">
         <v>25</v>
@@ -732,44 +718,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="5">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E11" s="5">
         <v>120</v>
       </c>
       <c r="G11">
         <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="4">
-        <v>17</v>
-      </c>
-      <c r="E12" s="4">
-        <v>120</v>
-      </c>
-      <c r="G12">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
